--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Academy: Introduction to Problem Solving (Intermediate) 1 &amp; 2</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Academy: Data Structures and Algorithms (Beginner)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Academy: Data Structures and Algorithms (Beginner)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Academy: Data Structures and Algorithms (Beginner)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Academy: Data Structures and Algorithms (Beginner)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Academy: Advanced DSA (Int/Adv)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Academy: Advanced DSA (Int/Adv)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Academy: Advanced DSA (Int/Adv)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Academy: Advanced DSA (Int/Adv)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Academy: Full-stack LLD and Development 4</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Data Engineering New Nov25</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Academy: DSA 4.2</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Academy: DSA for Competitive Programming</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -1314,16 +1314,8 @@
       <c r="Z39" s="43" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>Data Engineering</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Academy: Data Engineering (Old)</t>
-        </is>
-      </c>
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n"/>
       <c r="C40" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/21</t>
@@ -1422,16 +1414,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>Data Engineering</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Academy: Data Engineering (NA)</t>
-        </is>
-      </c>
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
       <c r="C45" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/532</t>
@@ -23887,7 +23871,11 @@
       <c r="C9" s="40" t="n">
         <v>71</v>
       </c>
-      <c r="D9" s="41" t="n"/>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/71</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="40" t="inlineStr">
@@ -23903,7 +23891,11 @@
       <c r="C10" s="40" t="n">
         <v>63</v>
       </c>
-      <c r="D10" s="41" t="n"/>
+      <c r="D10" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/63</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="40" t="inlineStr">

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -952,14 +952,10 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Academy: Advance Software Engineering (Beginner)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/410</t>
-        </is>
-      </c>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -955,7 +955,11 @@
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/410</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1976,17 +1980,13 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>AWS 1</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C11" s="19" t="n">
         <v>592</v>
       </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/592</t>
-        </is>
-      </c>
+      <c r="D11" s="25" t="n"/>
       <c r="E11" s="24" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2024,17 +2024,13 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>AWS 2</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C12" s="19" t="n">
         <v>593</v>
       </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/593</t>
-        </is>
-      </c>
+      <c r="D12" s="25" t="n"/>
       <c r="E12" s="24" t="inlineStr">
         <is>
           <t>Live</t>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z46"/>
+  <dimension ref="A1:Z76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="40.88" customWidth="1" style="46" min="1" max="1"/>
@@ -597,6 +597,11 @@
           <t>Library Link</t>
         </is>
       </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Num Attempts</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -633,77 +638,77 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Introduction to Programming (Beginner) 1</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Academy: Introduction to Programming (Beginner) 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/278</t>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>Introduction to Programming (Beginner) 1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Academy: Introduction to Programming (Beginner) 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/278</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
           <t>Introduction to Programming (Beginner) 2</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Academy: Introduction to Programming (Beginner) 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/278</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Introduction to Problem Solving (Intermediate) 1</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/11</t>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Problem Solving (Intermediate) 2</t>
+          <t>Introduction to Programming (Beginner) 2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Academy: Introduction to Problem Solving (Intermediate) 1 &amp; 2</t>
+          <t>Academy: Introduction to Programming (Beginner) 1 &amp; 2</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/11</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/278</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 1</t>
+          <t>Introduction to Problem Solving (Intermediate) 1</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -713,48 +718,48 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/281</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Data Structure Algorithms 2</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Problem Solving (Intermediate) 2</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/281</t>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 3</t>
+          <t>Introduction to Problem Solving (Intermediate) 2</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>NV Contests</t>
+          <t>Academy: Introduction to Problem Solving (Intermediate) 1 &amp; 2</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/281</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 4</t>
+          <t>Data Structure Algorithms 1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -771,7 +776,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Advanced DSA 1</t>
+          <t>Data Structure Algorithms 2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -781,14 +786,14 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/277</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/281</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Advanced DSA 2</t>
+          <t>Data Structure Algorithms 3</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -798,14 +803,14 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/277</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/281</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Advanced DSA 3</t>
+          <t>Data Structure Algorithms 4</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -815,14 +820,14 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/277</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/281</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Advanced DSA 4</t>
+          <t>Advanced DSA 1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -839,603 +844,1131 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Databases &amp; SQL</t>
+          <t>Advanced DSA 2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Academy: Databases and SQL (SEPT 2025)</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/713</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="n"/>
-      <c r="S16" s="4" t="n"/>
-      <c r="T16" s="4" t="n"/>
-      <c r="U16" s="4" t="n"/>
-      <c r="V16" s="4" t="n"/>
-      <c r="W16" s="4" t="n"/>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n"/>
-      <c r="Z16" s="4" t="n"/>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/277</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Advance Programming Concepts</t>
+          <t>Advanced DSA 3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Academy: Advance Programming Concepts (Beginner)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/343</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/277</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Advance Programming Concepts</t>
+          <t>Advanced DSA 4</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Academy: Python Advance Programming Concepts</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/417</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/277</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Low Level Design</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Academy: Low Level Design (Beginner)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/383</t>
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>Databases &amp; SQL</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Low Level Design</t>
+          <t>Databases &amp; SQL</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Academy: Python Low Level Design (2024)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/423</t>
-        </is>
-      </c>
+          <t>Academy: Databases and SQL (SEPT 2025)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/713</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="4" t="n"/>
+      <c r="S20" s="4" t="n"/>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
+      <c r="W20" s="4" t="n"/>
+      <c r="X20" s="4" t="n"/>
+      <c r="Y20" s="4" t="n"/>
+      <c r="Z20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Advance Software Engineering</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>Advance Programming Concepts</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/410</t>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Advance Software Engineering</t>
+          <t>Advance Programming Concepts</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Academy: Python Advance Software Engineering(2024)</t>
+          <t>Academy: Advance Programming Concepts (Beginner)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/467</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/343</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Backend Project</t>
+          <t>Advance Programming Concepts</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Academy: Backend Project (Beginner)</t>
+          <t>Academy: Python Advance Programming Concepts</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/320</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/417</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Backend Project</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Academy: Python Backend Project</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/398</t>
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>Low Level Design</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Backend LLD and Development 1</t>
+          <t>Low Level Design</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Academy: Backend LLD 1,2,3</t>
+          <t>Academy: Low Level Design (Beginner)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/128</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/383</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Backend LLD and Development 2</t>
+          <t>Low Level Design</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Academy: Backend LLD 1,2,3</t>
+          <t>Academy: Python Low Level Design (2024)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/128</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/423</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Backend LLD and Development 3</t>
+          <t>Advance Software Engineering</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Academy: Backend LLD 1,2,3</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/128</t>
-        </is>
+          <t>https://www.scaler.com/scm/classes/edit-library/410</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Backend Capstone Project</t>
+          <t>Advance Software Engineering</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Backend Capstone Project Latest (Dec2025)</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/757</t>
-        </is>
+          <t>Academy: Python Advance Software Engineering(2024)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/467</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Full-stack LLD and Development 1</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Academy: Full-stack LLD and Development 1</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/355</t>
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>Backend Project</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Full-stack LLD and Development 2</t>
+          <t>Backend Project</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Academy: Full-stack LLD and Development 2 (Beginners)</t>
+          <t>Academy: Backend Project (Beginner)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/356</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/320</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Full-stack LLD and Development 2</t>
+          <t>Backend Project</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Academy: Full-stack LLD and Development 2 (Int/Adv)</t>
+          <t>Academy: Python Backend Project</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/365</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/398</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Full-stack LLD and Development 3</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Academy: Full-stack LLD and Development 3</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/385</t>
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>Backend LLD and Development 1</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Full-stack LLD and Development 4</t>
+          <t>Backend LLD and Development 1</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>Academy: Backend LLD 1,2,3</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/128</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>Backend LLD and Development 2</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/386</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>High Level Design</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Academy: HLD (New)</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/647</t>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Product Management for Software Engineers</t>
+          <t>Backend LLD and Development 2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Academy: Product Management</t>
+          <t>Academy: Backend LLD 1,2,3</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/218</t>
-        </is>
+          <t>https://www.scaler.com/scm/classes/edit-library/128</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Data Engineering</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>Backend LLD and Development 3</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/751</t>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>Backend LLD and Development 3</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Academy: Backend LLD 1,2,3</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/128</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>Backend Capstone Project</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Backend Capstone Project</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Backend Capstone Project Latest (Dec2025)</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/757</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>Full-stack LLD and Development 1</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Full-stack LLD and Development 1</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Academy: Full-stack LLD and Development 1</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/355</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>Full-stack LLD and Development 2</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Full-stack LLD and Development 2</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Academy: Full-stack LLD and Development 2 (Beginners)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/356</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Full-stack LLD and Development 2</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Academy: Full-stack LLD and Development 2 (Int/Adv)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/365</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>Full-stack LLD and Development 3</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Full-stack LLD and Development 3</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Academy: Full-stack LLD and Development 3</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/385</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Full-stack LLD and Development 4</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/386</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>High Level Design</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>High Level Design</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Academy: HLD (New)</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/647</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>Product Management for Software Engineers</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Product Management for Software Engineers</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Academy: Product Management</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/218</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/751</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>DSA 4.2</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/291</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>DSA for Competitive Programming</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/2</t>
         </is>
       </c>
-      <c r="D38" s="43" t="n"/>
-      <c r="E38" s="43" t="n"/>
-      <c r="F38" s="43" t="n"/>
-      <c r="G38" s="43" t="n"/>
-      <c r="H38" s="43" t="n"/>
-      <c r="I38" s="43" t="n"/>
-      <c r="J38" s="43" t="n"/>
-      <c r="K38" s="43" t="n"/>
-      <c r="L38" s="43" t="n"/>
-      <c r="M38" s="43" t="n"/>
-      <c r="N38" s="43" t="n"/>
-      <c r="O38" s="43" t="n"/>
-      <c r="P38" s="43" t="n"/>
-      <c r="Q38" s="43" t="n"/>
-      <c r="R38" s="43" t="n"/>
-      <c r="S38" s="43" t="n"/>
-      <c r="T38" s="43" t="n"/>
-      <c r="U38" s="43" t="n"/>
-      <c r="V38" s="43" t="n"/>
-      <c r="W38" s="43" t="n"/>
-      <c r="X38" s="43" t="n"/>
-      <c r="Y38" s="43" t="n"/>
-      <c r="Z38" s="43" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="D54" s="43" t="n"/>
+      <c r="E54" s="43" t="n"/>
+      <c r="F54" s="43" t="n"/>
+      <c r="G54" s="43" t="n"/>
+      <c r="H54" s="43" t="n"/>
+      <c r="I54" s="43" t="n"/>
+      <c r="J54" s="43" t="n"/>
+      <c r="K54" s="43" t="n"/>
+      <c r="L54" s="43" t="n"/>
+      <c r="M54" s="43" t="n"/>
+      <c r="N54" s="43" t="n"/>
+      <c r="O54" s="43" t="n"/>
+      <c r="P54" s="43" t="n"/>
+      <c r="Q54" s="43" t="n"/>
+      <c r="R54" s="43" t="n"/>
+      <c r="S54" s="43" t="n"/>
+      <c r="T54" s="43" t="n"/>
+      <c r="U54" s="43" t="n"/>
+      <c r="V54" s="43" t="n"/>
+      <c r="W54" s="43" t="n"/>
+      <c r="X54" s="43" t="n"/>
+      <c r="Y54" s="43" t="n"/>
+      <c r="Z54" s="43" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Backend Capstone Project</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>Academy: Backend Capstone Project (Old-ongoing)</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/352</t>
         </is>
       </c>
-      <c r="D39" s="43" t="n"/>
-      <c r="E39" s="43" t="n"/>
-      <c r="F39" s="43" t="n"/>
-      <c r="G39" s="43" t="n"/>
-      <c r="H39" s="43" t="n"/>
-      <c r="I39" s="43" t="n"/>
-      <c r="J39" s="43" t="n"/>
-      <c r="K39" s="43" t="n"/>
-      <c r="L39" s="43" t="n"/>
-      <c r="M39" s="43" t="n"/>
-      <c r="N39" s="43" t="n"/>
-      <c r="O39" s="43" t="n"/>
-      <c r="P39" s="43" t="n"/>
-      <c r="Q39" s="43" t="n"/>
-      <c r="R39" s="43" t="n"/>
-      <c r="S39" s="43" t="n"/>
-      <c r="T39" s="43" t="n"/>
-      <c r="U39" s="43" t="n"/>
-      <c r="V39" s="43" t="n"/>
-      <c r="W39" s="43" t="n"/>
-      <c r="X39" s="43" t="n"/>
-      <c r="Y39" s="43" t="n"/>
-      <c r="Z39" s="43" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="n"/>
-      <c r="B40" s="9" t="n"/>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="D55" s="43" t="n"/>
+      <c r="E55" s="43" t="n"/>
+      <c r="F55" s="43" t="n"/>
+      <c r="G55" s="43" t="n"/>
+      <c r="H55" s="43" t="n"/>
+      <c r="I55" s="43" t="n"/>
+      <c r="J55" s="43" t="n"/>
+      <c r="K55" s="43" t="n"/>
+      <c r="L55" s="43" t="n"/>
+      <c r="M55" s="43" t="n"/>
+      <c r="N55" s="43" t="n"/>
+      <c r="O55" s="43" t="n"/>
+      <c r="P55" s="43" t="n"/>
+      <c r="Q55" s="43" t="n"/>
+      <c r="R55" s="43" t="n"/>
+      <c r="S55" s="43" t="n"/>
+      <c r="T55" s="43" t="n"/>
+      <c r="U55" s="43" t="n"/>
+      <c r="V55" s="43" t="n"/>
+      <c r="W55" s="43" t="n"/>
+      <c r="X55" s="43" t="n"/>
+      <c r="Y55" s="43" t="n"/>
+      <c r="Z55" s="43" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/21</t>
         </is>
       </c>
-      <c r="D40" s="43" t="n"/>
-      <c r="E40" s="43" t="n"/>
-      <c r="F40" s="43" t="n"/>
-      <c r="G40" s="43" t="n"/>
-      <c r="H40" s="43" t="n"/>
-      <c r="I40" s="43" t="n"/>
-      <c r="J40" s="43" t="n"/>
-      <c r="K40" s="43" t="n"/>
-      <c r="L40" s="43" t="n"/>
-      <c r="M40" s="43" t="n"/>
-      <c r="N40" s="43" t="n"/>
-      <c r="O40" s="43" t="n"/>
-      <c r="P40" s="43" t="n"/>
-      <c r="Q40" s="43" t="n"/>
-      <c r="R40" s="43" t="n"/>
-      <c r="S40" s="43" t="n"/>
-      <c r="T40" s="43" t="n"/>
-      <c r="U40" s="43" t="n"/>
-      <c r="V40" s="43" t="n"/>
-      <c r="W40" s="43" t="n"/>
-      <c r="X40" s="43" t="n"/>
-      <c r="Y40" s="43" t="n"/>
-      <c r="Z40" s="43" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="D56" s="43" t="n"/>
+      <c r="E56" s="43" t="n"/>
+      <c r="F56" s="43" t="n"/>
+      <c r="G56" s="43" t="n"/>
+      <c r="H56" s="43" t="n"/>
+      <c r="I56" s="43" t="n"/>
+      <c r="J56" s="43" t="n"/>
+      <c r="K56" s="43" t="n"/>
+      <c r="L56" s="43" t="n"/>
+      <c r="M56" s="43" t="n"/>
+      <c r="N56" s="43" t="n"/>
+      <c r="O56" s="43" t="n"/>
+      <c r="P56" s="43" t="n"/>
+      <c r="Q56" s="43" t="n"/>
+      <c r="R56" s="43" t="n"/>
+      <c r="S56" s="43" t="n"/>
+      <c r="T56" s="43" t="n"/>
+      <c r="U56" s="43" t="n"/>
+      <c r="V56" s="43" t="n"/>
+      <c r="W56" s="43" t="n"/>
+      <c r="X56" s="43" t="n"/>
+      <c r="Y56" s="43" t="n"/>
+      <c r="Z56" s="43" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>High Level Design</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Academy: HLD (Intermediate + Advanced + Beginner)</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/20</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Databases &amp; SQL</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>Academy: SQL (Oldv2)</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/408</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Databases &amp; SQL</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>Academy: SQL Inverted (NA)</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/409</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Backend Capstone Project</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Academy: Backend Capstone Project Inverted (NA) </t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/575</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="7" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/532</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>Backend Capstone Project</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>Academy: Backend Capstone Project (NA)</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/238</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>Backend LLD and Development 4</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t>Advanced AI Agents</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>Basics of GenAI and AI agents</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>Common Core Fundamentals</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>Common Core tools</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>Common Core Foundations</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>Common Core Maths</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t>Computer Systems and Fundamentals</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t>LLD: Object Oriented Design and Analysis</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t>LLD: Practical Software Engineering and Design</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>Full-Stack Capstone Project</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>Full-stack Capstone Project</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>Front-end Development</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>Back-end development</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
@@ -1986,7 +2519,11 @@
       <c r="C11" s="19" t="n">
         <v>592</v>
       </c>
-      <c r="D11" s="25" t="n"/>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/592</t>
+        </is>
+      </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2030,7 +2567,11 @@
       <c r="C12" s="19" t="n">
         <v>593</v>
       </c>
-      <c r="D12" s="25" t="n"/>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/593</t>
+        </is>
+      </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
           <t>Live</t>
@@ -23601,7 +24142,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="43" customWidth="1" style="46" min="1" max="1"/>
@@ -23666,46 +24207,24 @@
       <c r="Z1" s="37" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>SQL</t>
         </is>
       </c>
-      <c r="B2" s="38" t="inlineStr">
-        <is>
-          <t>SQL: New (DSML)</t>
-        </is>
-      </c>
-      <c r="C2" s="38" t="n">
-        <v>712</v>
-      </c>
-      <c r="D2" s="39" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/712</t>
-        </is>
-      </c>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-      <c r="M2" s="38" t="n"/>
-      <c r="N2" s="38" t="n"/>
-      <c r="O2" s="38" t="n"/>
-      <c r="P2" s="38" t="n"/>
-      <c r="Q2" s="38" t="n"/>
-      <c r="R2" s="38" t="n"/>
-      <c r="S2" s="38" t="n"/>
-      <c r="T2" s="38" t="n"/>
-      <c r="U2" s="38" t="n"/>
-      <c r="V2" s="38" t="n"/>
-      <c r="W2" s="38" t="n"/>
-      <c r="X2" s="38" t="n"/>
-      <c r="Y2" s="38" t="n"/>
-      <c r="Z2" s="38" t="n"/>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="38" t="inlineStr">
@@ -23715,15 +24234,15 @@
       </c>
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>Long-format SQL: New (DSML)</t>
+          <t>SQL: New (DSML)</t>
         </is>
       </c>
       <c r="C3" s="38" t="n">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/717</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/712</t>
         </is>
       </c>
       <c r="E3" s="38" t="n"/>
@@ -23750,422 +24269,1475 @@
       <c r="Z3" s="38" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>Long-format SQL: New (DSML)</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="n">
+        <v>717</v>
+      </c>
+      <c r="D4" s="39" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/717</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="n"/>
+      <c r="F4" s="38" t="n"/>
+      <c r="G4" s="38" t="n"/>
+      <c r="H4" s="38" t="n"/>
+      <c r="I4" s="38" t="n"/>
+      <c r="J4" s="38" t="n"/>
+      <c r="K4" s="38" t="n"/>
+      <c r="L4" s="38" t="n"/>
+      <c r="M4" s="38" t="n"/>
+      <c r="N4" s="38" t="n"/>
+      <c r="O4" s="38" t="n"/>
+      <c r="P4" s="38" t="n"/>
+      <c r="Q4" s="38" t="n"/>
+      <c r="R4" s="38" t="n"/>
+      <c r="S4" s="38" t="n"/>
+      <c r="T4" s="38" t="n"/>
+      <c r="U4" s="38" t="n"/>
+      <c r="V4" s="38" t="n"/>
+      <c r="W4" s="38" t="n"/>
+      <c r="X4" s="38" t="n"/>
+      <c r="Y4" s="38" t="n"/>
+      <c r="Z4" s="38" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Tableau and Excel</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>Tableau and Excel</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Tableau and Excel Long Version</t>
         </is>
       </c>
-      <c r="C4" s="40" t="n">
+      <c r="C6" s="40" t="n">
         <v>46</v>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/46</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>Tableau and Excel</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>Tableau and Excel Short Version</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>638</v>
+      </c>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/638</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Beginner Python 1</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>Beginner Python 1</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>Beginner Python 1 Inverted</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>172</v>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/172</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>Beginner Python 2</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>Beginner Python 2</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>Beginner Python 2 Inverted</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="n">
+        <v>561</v>
+      </c>
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/561</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>Data Analytics and Visualisation - Python Libraries</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>Data Analytics and Visualisation - Python Libraries</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>Data Analytics and Visualisation - Python Libraries</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="n">
+        <v>227</v>
+      </c>
+      <c r="D13" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/227</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>Data Analytics and Visualisation - Probability and Stats</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>71</v>
+      </c>
+      <c r="D14" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/71</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>Data Analytics and Visualisation - Fundamentals</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>63</v>
+      </c>
+      <c r="D15" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/63</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>Product Analytics</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>Product Analytics</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>Product Analytics</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="n">
+        <v>44</v>
+      </c>
+      <c r="D17" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/44</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>Maths for ML</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>Maths for ML</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>Maths for ML</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="n">
+        <v>47</v>
+      </c>
+      <c r="D19" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/47</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>Intro to ML and NN</t>
+        </is>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="n">
+        <v>60</v>
+      </c>
+      <c r="D20" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>ML : Supervised Algorithms</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>ML : Supervised Algorithms</t>
+        </is>
+      </c>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t>ML : Supervised Algorithms</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="n">
+        <v>52</v>
+      </c>
+      <c r="D22" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/52</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>ML : Adv Supervised Algorithms</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>ML : Adv Supervised Algorithms</t>
+        </is>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>ML : Adv Supervised Algorithms</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="n">
+        <v>414</v>
+      </c>
+      <c r="D24" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/414</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>ML : Unsupervised and RecSys</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>ML : Unsupervised and RecSys</t>
+        </is>
+      </c>
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>ML : Unsupervised and RecSys</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="n">
+        <v>57</v>
+      </c>
+      <c r="D26" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/57</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="n">
+        <v>50</v>
+      </c>
+      <c r="D28" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>Neural Networks</t>
+        </is>
+      </c>
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="n">
+        <v>60</v>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>Computer Vision</t>
+        </is>
+      </c>
+      <c r="B30" s="40" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="n">
+        <v>60</v>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/60</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="n">
+        <v>61</v>
+      </c>
+      <c r="D32" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/61</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>Advanced Python</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>Advanced Python</t>
+        </is>
+      </c>
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>Advanced Python</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="n">
+        <v>56</v>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/56</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="inlineStr">
+        <is>
+          <t>DA Portfolio Project</t>
+        </is>
+      </c>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>DSML DA Portfolio Project</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="n">
+        <v>501</v>
+      </c>
+      <c r="D35" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/501</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="inlineStr">
+        <is>
+          <t>DS Portfolio Project</t>
+        </is>
+      </c>
+      <c r="B36" s="40" t="inlineStr">
+        <is>
+          <t>DSML DS Portfolio Project New</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="n">
+        <v>323</v>
+      </c>
+      <c r="D36" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/323</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>DSML Extra : SQL</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="n">
+        <v>97</v>
+      </c>
+      <c r="D37" s="44" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/97</t>
+        </is>
+      </c>
+      <c r="E37" s="43" t="n"/>
+      <c r="F37" s="43" t="n"/>
+      <c r="G37" s="43" t="n"/>
+      <c r="H37" s="43" t="n"/>
+      <c r="I37" s="43" t="n"/>
+      <c r="J37" s="43" t="n"/>
+      <c r="K37" s="43" t="n"/>
+      <c r="L37" s="43" t="n"/>
+      <c r="M37" s="43" t="n"/>
+      <c r="N37" s="43" t="n"/>
+      <c r="O37" s="43" t="n"/>
+      <c r="P37" s="43" t="n"/>
+      <c r="Q37" s="43" t="n"/>
+      <c r="R37" s="43" t="n"/>
+      <c r="S37" s="43" t="n"/>
+      <c r="T37" s="43" t="n"/>
+      <c r="U37" s="43" t="n"/>
+      <c r="V37" s="43" t="n"/>
+      <c r="W37" s="43" t="n"/>
+      <c r="X37" s="43" t="n"/>
+      <c r="Y37" s="43" t="n"/>
+      <c r="Z37" s="43" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>DSML Extra Misc</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="n">
+        <v>110</v>
+      </c>
+      <c r="D38" s="44" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/110</t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="n"/>
+      <c r="F38" s="43" t="n"/>
+      <c r="G38" s="43" t="n"/>
+      <c r="H38" s="43" t="n"/>
+      <c r="I38" s="43" t="n"/>
+      <c r="J38" s="43" t="n"/>
+      <c r="K38" s="43" t="n"/>
+      <c r="L38" s="43" t="n"/>
+      <c r="M38" s="43" t="n"/>
+      <c r="N38" s="43" t="n"/>
+      <c r="O38" s="43" t="n"/>
+      <c r="P38" s="43" t="n"/>
+      <c r="Q38" s="43" t="n"/>
+      <c r="R38" s="43" t="n"/>
+      <c r="S38" s="43" t="n"/>
+      <c r="T38" s="43" t="n"/>
+      <c r="U38" s="43" t="n"/>
+      <c r="V38" s="43" t="n"/>
+      <c r="W38" s="43" t="n"/>
+      <c r="X38" s="43" t="n"/>
+      <c r="Y38" s="43" t="n"/>
+      <c r="Z38" s="43" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>SQL Library Long Version</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="n">
+        <v>165</v>
+      </c>
+      <c r="D39" s="44" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/165</t>
+        </is>
+      </c>
+      <c r="E39" s="43" t="n"/>
+      <c r="F39" s="43" t="n"/>
+      <c r="G39" s="43" t="n"/>
+      <c r="H39" s="43" t="n"/>
+      <c r="I39" s="43" t="n"/>
+      <c r="J39" s="43" t="n"/>
+      <c r="K39" s="43" t="n"/>
+      <c r="L39" s="43" t="n"/>
+      <c r="M39" s="43" t="n"/>
+      <c r="N39" s="43" t="n"/>
+      <c r="O39" s="43" t="n"/>
+      <c r="P39" s="43" t="n"/>
+      <c r="Q39" s="43" t="n"/>
+      <c r="R39" s="43" t="n"/>
+      <c r="S39" s="43" t="n"/>
+      <c r="T39" s="43" t="n"/>
+      <c r="U39" s="43" t="n"/>
+      <c r="V39" s="43" t="n"/>
+      <c r="W39" s="43" t="n"/>
+      <c r="X39" s="43" t="n"/>
+      <c r="Y39" s="43" t="n"/>
+      <c r="Z39" s="43" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>SQL Library Short Version</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="n">
+        <v>639</v>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/639</t>
+        </is>
+      </c>
+      <c r="E40" s="43" t="n"/>
+      <c r="F40" s="43" t="n"/>
+      <c r="G40" s="43" t="n"/>
+      <c r="H40" s="43" t="n"/>
+      <c r="I40" s="43" t="n"/>
+      <c r="J40" s="43" t="n"/>
+      <c r="K40" s="43" t="n"/>
+      <c r="L40" s="43" t="n"/>
+      <c r="M40" s="43" t="n"/>
+      <c r="N40" s="43" t="n"/>
+      <c r="O40" s="43" t="n"/>
+      <c r="P40" s="43" t="n"/>
+      <c r="Q40" s="43" t="n"/>
+      <c r="R40" s="43" t="n"/>
+      <c r="S40" s="43" t="n"/>
+      <c r="T40" s="43" t="n"/>
+      <c r="U40" s="43" t="n"/>
+      <c r="V40" s="43" t="n"/>
+      <c r="W40" s="43" t="n"/>
+      <c r="X40" s="43" t="n"/>
+      <c r="Y40" s="43" t="n"/>
+      <c r="Z40" s="43" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>Classical ML 1</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>DA ML 1</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>DA ML 2</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>Advanced SQL</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId25"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z24"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="42.25" customWidth="1" style="46" min="1" max="1"/>
+    <col width="77.5" customWidth="1" style="46" min="2" max="2"/>
+    <col width="48.88" customWidth="1" style="46" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module Name </t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Library Name </t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Library id</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contest link </t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Months</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>Data Foundations</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>Data Foundations</t>
+        </is>
+      </c>
+      <c r="B3" s="40" t="inlineStr">
+        <is>
+          <t>Data Foundations (Jan 2026)</t>
+        </is>
+      </c>
+      <c r="C3" s="40" t="n">
+        <v>768</v>
+      </c>
+      <c r="D3" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/768</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>ML Coding: Supervised Learning</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="40" t="inlineStr">
         <is>
-          <t>Tableau and Excel</t>
+          <t>ML Coding: Supervised Learning</t>
         </is>
       </c>
       <c r="B5" s="40" t="inlineStr">
         <is>
-          <t>Tableau and Excel Short Version</t>
+          <t>ML Coding: Supervised Learning</t>
         </is>
       </c>
       <c r="C5" s="40" t="n">
-        <v>638</v>
+        <v>702</v>
       </c>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/638</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/702</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
-        <is>
-          <t>Beginner Python 1</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>Beginner Python 1 Inverted</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="n">
-        <v>172</v>
-      </c>
-      <c r="D6" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/172</t>
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>ML Coding: Unsupervised Learning, Time series &amp; Recommender Systems</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="40" t="inlineStr">
         <is>
-          <t>Beginner Python 2</t>
+          <t>ML Coding: Unsupervised Learning, Time series &amp; Recommender Systems</t>
         </is>
       </c>
       <c r="B7" s="40" t="inlineStr">
         <is>
-          <t>Beginner Python 2 Inverted</t>
+          <t>ML Coding: Unsupervised Learning, Time series &amp; Recommender Systems</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>561</v>
+        <v>703</v>
       </c>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/561</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/703</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
-        <is>
-          <t>Data Analytics and Visualisation - Python Libraries</t>
-        </is>
-      </c>
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>Data Analytics and Visualisation - Python Libraries</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="n">
-        <v>227</v>
-      </c>
-      <c r="D8" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/227</t>
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>MLCoding: Neural Networks</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>Data Analytics and Visualisation - Probability and Stats</t>
+          <t>MLCoding: Neural Networks</t>
         </is>
       </c>
       <c r="B9" s="40" t="inlineStr">
         <is>
+          <t>MLCoding: Neural Networks</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>704</v>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/704</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>MLCoding: Computer Vision and Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C9" s="40" t="n">
-        <v>71</v>
-      </c>
-      <c r="D9" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/71</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="40" t="inlineStr">
-        <is>
-          <t>Data Analytics and Visualisation - Fundamentals</t>
-        </is>
-      </c>
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>NV Contests</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="n">
-        <v>63</v>
-      </c>
-      <c r="D10" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/63</t>
+      <c r="C10" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="40" t="inlineStr">
         <is>
-          <t>Product Analytics</t>
+          <t>MLCoding: Computer Vision and Natural Language Processing</t>
         </is>
       </c>
       <c r="B11" s="40" t="inlineStr">
         <is>
-          <t>Product Analytics</t>
+          <t>MLCoding: Computer Vision and Natural Language Processing</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>44</v>
+        <v>705</v>
       </c>
       <c r="D11" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/44</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/705</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="40" t="inlineStr">
         <is>
-          <t>Maths for ML</t>
+          <t>MLOPS (AIML)</t>
         </is>
       </c>
       <c r="B12" s="40" t="inlineStr">
         <is>
-          <t>Maths for ML</t>
+          <t>MLOPS (AIML)</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>47</v>
+        <v>706</v>
       </c>
       <c r="D12" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/47</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/706</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="40" t="inlineStr">
         <is>
-          <t>Intro to ML and NN</t>
+          <t>ML System Design</t>
         </is>
       </c>
       <c r="B13" s="40" t="inlineStr">
         <is>
-          <t>Intro to ML and NN</t>
+          <t>ML System Design</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>36</v>
+        <v>707</v>
       </c>
       <c r="D13" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/36</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/707</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
-        <is>
-          <t>ML : Supervised Algorithms</t>
-        </is>
-      </c>
-      <c r="B14" s="40" t="inlineStr">
-        <is>
-          <t>ML : Supervised Algorithms</t>
-        </is>
-      </c>
-      <c r="C14" s="40" t="n">
-        <v>52</v>
-      </c>
-      <c r="D14" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/52</t>
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>Basics of GenAI and AI agents (AIML)</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="40" t="inlineStr">
         <is>
-          <t>ML : Adv Supervised Algorithms</t>
+          <t>Basics of GenAI and AI agents (AIML)</t>
         </is>
       </c>
       <c r="B15" s="40" t="inlineStr">
         <is>
-          <t>ML : Adv Supervised Algorithms</t>
+          <t>Basics of GenAI and AI agents</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>414</v>
+        <v>708</v>
       </c>
       <c r="D15" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/414</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/708</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
-        <is>
-          <t>ML : Unsupervised and RecSys</t>
-        </is>
-      </c>
-      <c r="B16" s="40" t="inlineStr">
-        <is>
-          <t>ML : Unsupervised and RecSys</t>
-        </is>
-      </c>
-      <c r="C16" s="40" t="n">
-        <v>57</v>
-      </c>
-      <c r="D16" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/57</t>
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>Advanced AI Agents (AIML)</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="40" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Advanced AI Agents (AIML)</t>
         </is>
       </c>
       <c r="B17" s="40" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Advanced AI Agents</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>50</v>
+        <v>709</v>
       </c>
       <c r="D17" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/50</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/709</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="40" t="inlineStr">
         <is>
-          <t>Neural Networks</t>
+          <t>LLMOPS (Recorded)</t>
         </is>
       </c>
       <c r="B18" s="40" t="inlineStr">
         <is>
-          <t>Neural Networks</t>
+          <t>LLMOPS (Recorded)</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>58</v>
+        <v>710</v>
       </c>
       <c r="D18" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/58</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/710</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="40" t="inlineStr">
         <is>
-          <t>Computer Vision</t>
+          <t>Reinforcement learning</t>
         </is>
       </c>
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>Computer Vision</t>
+          <t>Reinforcement learning</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>60</v>
+        <v>711</v>
       </c>
       <c r="D19" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/60</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/711</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="40" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
+          <t>DSA for Professionals 1,2,3,4</t>
         </is>
       </c>
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
+          <t>DSA for Professionals 1,2,3,4</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>61</v>
-      </c>
-      <c r="D20" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/61</t>
+        <v>630</v>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/630</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="40" t="inlineStr">
         <is>
-          <t>Advanced Python</t>
+          <t>Agentic AI Systems</t>
         </is>
       </c>
       <c r="B21" s="40" t="inlineStr">
         <is>
-          <t>Advanced Python</t>
+          <t>AIML : Agentic AI Systems (Feb 2026)</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>56</v>
+        <v>786</v>
       </c>
       <c r="D21" s="42" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/56</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/786</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
-        <is>
-          <t>DA Portfolio Project</t>
-        </is>
-      </c>
-      <c r="B22" s="40" t="inlineStr">
-        <is>
-          <t>DSML DA Portfolio Project</t>
-        </is>
-      </c>
-      <c r="C22" s="40" t="n">
-        <v>501</v>
-      </c>
-      <c r="D22" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/501</t>
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>Maths for ML (AIML)</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="40" t="inlineStr">
         <is>
-          <t>DS Portfolio Project</t>
+          <t>Maths for ML (AIML)</t>
         </is>
       </c>
       <c r="B23" s="40" t="inlineStr">
         <is>
-          <t>DSML DS Portfolio Project New</t>
+          <t>AIML Maths for ML</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>323</v>
-      </c>
-      <c r="D23" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/323</t>
+        <v>602</v>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/602</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="43" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Data Foundations</t>
         </is>
       </c>
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t>DSML Extra : SQL</t>
+          <t>Data Foundations (NA)</t>
         </is>
       </c>
       <c r="C24" s="43" t="n">
-        <v>97</v>
+        <v>701</v>
       </c>
       <c r="D24" s="44" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/97</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/701</t>
         </is>
       </c>
       <c r="E24" s="43" t="n"/>
@@ -24190,538 +25762,6 @@
       <c r="X24" s="43" t="n"/>
       <c r="Y24" s="43" t="n"/>
       <c r="Z24" s="43" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="43" t="inlineStr">
-        <is>
-          <t>Misc</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="inlineStr">
-        <is>
-          <t>DSML Extra Misc</t>
-        </is>
-      </c>
-      <c r="C25" s="43" t="n">
-        <v>110</v>
-      </c>
-      <c r="D25" s="44" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/110</t>
-        </is>
-      </c>
-      <c r="E25" s="43" t="n"/>
-      <c r="F25" s="43" t="n"/>
-      <c r="G25" s="43" t="n"/>
-      <c r="H25" s="43" t="n"/>
-      <c r="I25" s="43" t="n"/>
-      <c r="J25" s="43" t="n"/>
-      <c r="K25" s="43" t="n"/>
-      <c r="L25" s="43" t="n"/>
-      <c r="M25" s="43" t="n"/>
-      <c r="N25" s="43" t="n"/>
-      <c r="O25" s="43" t="n"/>
-      <c r="P25" s="43" t="n"/>
-      <c r="Q25" s="43" t="n"/>
-      <c r="R25" s="43" t="n"/>
-      <c r="S25" s="43" t="n"/>
-      <c r="T25" s="43" t="n"/>
-      <c r="U25" s="43" t="n"/>
-      <c r="V25" s="43" t="n"/>
-      <c r="W25" s="43" t="n"/>
-      <c r="X25" s="43" t="n"/>
-      <c r="Y25" s="43" t="n"/>
-      <c r="Z25" s="43" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="43" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
-      <c r="B26" s="43" t="inlineStr">
-        <is>
-          <t>SQL Library Long Version</t>
-        </is>
-      </c>
-      <c r="C26" s="43" t="n">
-        <v>165</v>
-      </c>
-      <c r="D26" s="44" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/165</t>
-        </is>
-      </c>
-      <c r="E26" s="43" t="n"/>
-      <c r="F26" s="43" t="n"/>
-      <c r="G26" s="43" t="n"/>
-      <c r="H26" s="43" t="n"/>
-      <c r="I26" s="43" t="n"/>
-      <c r="J26" s="43" t="n"/>
-      <c r="K26" s="43" t="n"/>
-      <c r="L26" s="43" t="n"/>
-      <c r="M26" s="43" t="n"/>
-      <c r="N26" s="43" t="n"/>
-      <c r="O26" s="43" t="n"/>
-      <c r="P26" s="43" t="n"/>
-      <c r="Q26" s="43" t="n"/>
-      <c r="R26" s="43" t="n"/>
-      <c r="S26" s="43" t="n"/>
-      <c r="T26" s="43" t="n"/>
-      <c r="U26" s="43" t="n"/>
-      <c r="V26" s="43" t="n"/>
-      <c r="W26" s="43" t="n"/>
-      <c r="X26" s="43" t="n"/>
-      <c r="Y26" s="43" t="n"/>
-      <c r="Z26" s="43" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="43" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
-      <c r="B27" s="43" t="inlineStr">
-        <is>
-          <t>SQL Library Short Version</t>
-        </is>
-      </c>
-      <c r="C27" s="43" t="n">
-        <v>639</v>
-      </c>
-      <c r="D27" s="44" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/639</t>
-        </is>
-      </c>
-      <c r="E27" s="43" t="n"/>
-      <c r="F27" s="43" t="n"/>
-      <c r="G27" s="43" t="n"/>
-      <c r="H27" s="43" t="n"/>
-      <c r="I27" s="43" t="n"/>
-      <c r="J27" s="43" t="n"/>
-      <c r="K27" s="43" t="n"/>
-      <c r="L27" s="43" t="n"/>
-      <c r="M27" s="43" t="n"/>
-      <c r="N27" s="43" t="n"/>
-      <c r="O27" s="43" t="n"/>
-      <c r="P27" s="43" t="n"/>
-      <c r="Q27" s="43" t="n"/>
-      <c r="R27" s="43" t="n"/>
-      <c r="S27" s="43" t="n"/>
-      <c r="T27" s="43" t="n"/>
-      <c r="U27" s="43" t="n"/>
-      <c r="V27" s="43" t="n"/>
-      <c r="W27" s="43" t="n"/>
-      <c r="X27" s="43" t="n"/>
-      <c r="Y27" s="43" t="n"/>
-      <c r="Z27" s="43" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="42.25" customWidth="1" style="46" min="1" max="1"/>
-    <col width="77.5" customWidth="1" style="46" min="2" max="2"/>
-    <col width="48.88" customWidth="1" style="46" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Module Name </t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Library Name </t>
-        </is>
-      </c>
-      <c r="C1" s="11" t="inlineStr">
-        <is>
-          <t>Library id</t>
-        </is>
-      </c>
-      <c r="D1" s="11" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="E1" s="11" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contest link </t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Months</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="40" t="inlineStr">
-        <is>
-          <t>Data Foundations</t>
-        </is>
-      </c>
-      <c r="B2" s="40" t="inlineStr">
-        <is>
-          <t>Data Foundations (Jan 2026)</t>
-        </is>
-      </c>
-      <c r="C2" s="40" t="n">
-        <v>768</v>
-      </c>
-      <c r="D2" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/768</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="40" t="inlineStr">
-        <is>
-          <t>ML Coding: Supervised Learning</t>
-        </is>
-      </c>
-      <c r="B3" s="40" t="inlineStr">
-        <is>
-          <t>ML Coding: Supervised Learning</t>
-        </is>
-      </c>
-      <c r="C3" s="40" t="n">
-        <v>702</v>
-      </c>
-      <c r="D3" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/702</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="40" t="inlineStr">
-        <is>
-          <t>ML Coding: Unsupervised Learning, Time series &amp; Recommender Systems</t>
-        </is>
-      </c>
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>ML Coding: Unsupervised Learning, Time series &amp; Recommender Systems</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="n">
-        <v>703</v>
-      </c>
-      <c r="D4" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/703</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="40" t="inlineStr">
-        <is>
-          <t>MLCoding: Neural Networks</t>
-        </is>
-      </c>
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>MLCoding: Neural Networks</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="n">
-        <v>704</v>
-      </c>
-      <c r="D5" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/704</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="40" t="inlineStr">
-        <is>
-          <t>MLCoding: Computer Vision and Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>MLCoding: Computer Vision and Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="n">
-        <v>705</v>
-      </c>
-      <c r="D6" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/705</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="40" t="inlineStr">
-        <is>
-          <t>MLOPS (AIML)</t>
-        </is>
-      </c>
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>MLOPS (AIML)</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="n">
-        <v>706</v>
-      </c>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/706</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
-        <is>
-          <t>ML System Design</t>
-        </is>
-      </c>
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>ML System Design</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="n">
-        <v>707</v>
-      </c>
-      <c r="D8" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/707</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="40" t="inlineStr">
-        <is>
-          <t>Basics of GenAI and AI agents</t>
-        </is>
-      </c>
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>Basics of GenAI and AI agents</t>
-        </is>
-      </c>
-      <c r="C9" s="40" t="n">
-        <v>708</v>
-      </c>
-      <c r="D9" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/708</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="40" t="inlineStr">
-        <is>
-          <t>Advanced AI Agents</t>
-        </is>
-      </c>
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>Advanced AI Agents</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="n">
-        <v>709</v>
-      </c>
-      <c r="D10" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/709</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="40" t="inlineStr">
-        <is>
-          <t>LLMOPS (Recorded)</t>
-        </is>
-      </c>
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>LLMOPS (Recorded)</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="n">
-        <v>710</v>
-      </c>
-      <c r="D11" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/710</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="40" t="inlineStr">
-        <is>
-          <t>Reinforcement learning</t>
-        </is>
-      </c>
-      <c r="B12" s="40" t="inlineStr">
-        <is>
-          <t>Reinforcement learning</t>
-        </is>
-      </c>
-      <c r="C12" s="40" t="n">
-        <v>711</v>
-      </c>
-      <c r="D12" s="41" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/711</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="40" t="inlineStr">
-        <is>
-          <t>DSA for Professionals 1,2,3,4</t>
-        </is>
-      </c>
-      <c r="B13" s="40" t="inlineStr">
-        <is>
-          <t>DSA for Professionals 1,2,3,4</t>
-        </is>
-      </c>
-      <c r="C13" s="40" t="n">
-        <v>630</v>
-      </c>
-      <c r="D13" s="42" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/630</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="40" t="inlineStr">
-        <is>
-          <t>Agentic AI Systems</t>
-        </is>
-      </c>
-      <c r="B14" s="40" t="inlineStr">
-        <is>
-          <t>AIML : Agentic AI Systems (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="C14" s="40" t="n">
-        <v>786</v>
-      </c>
-      <c r="D14" s="42" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/786</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="40" t="inlineStr">
-        <is>
-          <t>Maths for ML (AIML)</t>
-        </is>
-      </c>
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>AIML Maths for ML</t>
-        </is>
-      </c>
-      <c r="C15" s="40" t="n">
-        <v>602</v>
-      </c>
-      <c r="D15" s="42" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/602</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>Data Foundations</t>
-        </is>
-      </c>
-      <c r="B16" s="43" t="inlineStr">
-        <is>
-          <t>Data Foundations (NA)</t>
-        </is>
-      </c>
-      <c r="C16" s="43" t="n">
-        <v>701</v>
-      </c>
-      <c r="D16" s="44" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/701</t>
-        </is>
-      </c>
-      <c r="E16" s="43" t="n"/>
-      <c r="F16" s="43" t="n"/>
-      <c r="G16" s="43" t="n"/>
-      <c r="H16" s="43" t="n"/>
-      <c r="I16" s="43" t="n"/>
-      <c r="J16" s="43" t="n"/>
-      <c r="K16" s="43" t="n"/>
-      <c r="L16" s="43" t="n"/>
-      <c r="M16" s="43" t="n"/>
-      <c r="N16" s="43" t="n"/>
-      <c r="O16" s="43" t="n"/>
-      <c r="P16" s="43" t="n"/>
-      <c r="Q16" s="43" t="n"/>
-      <c r="R16" s="43" t="n"/>
-      <c r="S16" s="43" t="n"/>
-      <c r="T16" s="43" t="n"/>
-      <c r="U16" s="43" t="n"/>
-      <c r="V16" s="43" t="n"/>
-      <c r="W16" s="43" t="n"/>
-      <c r="X16" s="43" t="n"/>
-      <c r="Y16" s="43" t="n"/>
-      <c r="Z16" s="43" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -2031,7 +2031,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1007"/>
+  <dimension ref="A1:Z1008"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="41.63" customWidth="1" style="46" min="1" max="1"/>
@@ -2096,50 +2096,29 @@
       <c r="Z1" s="38" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Beginner Python </t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="inlineStr">
-        <is>
-          <t>Devops: Beginner Python (New)</t>
-        </is>
-      </c>
-      <c r="C2" s="19" t="n">
-        <v>653</v>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/653</t>
-        </is>
-      </c>
-      <c r="E2" s="24" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Linux Shell Scripting and Computer Systems 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>338</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
       </c>
-      <c r="F2" s="24" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-      <c r="M2" s="38" t="n"/>
-      <c r="N2" s="38" t="n"/>
-      <c r="O2" s="38" t="n"/>
-      <c r="P2" s="38" t="n"/>
-      <c r="Q2" s="38" t="n"/>
-      <c r="R2" s="38" t="n"/>
-      <c r="S2" s="38" t="n"/>
-      <c r="T2" s="38" t="n"/>
-      <c r="U2" s="38" t="n"/>
-      <c r="V2" s="38" t="n"/>
-      <c r="W2" s="38" t="n"/>
-      <c r="X2" s="38" t="n"/>
-      <c r="Y2" s="38" t="n"/>
-      <c r="Z2" s="38" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
@@ -2149,18 +2128,18 @@
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>Devops: Beginner Python with Breaks (New)</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="n">
-        <v>667</v>
+          <t>Devops: Beginner Python (New)</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>653</v>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/667</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
+          <t>https://www.scaler.com/scm/classes/edit-library/653</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -2190,20 +2169,20 @@
     <row r="4">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 1</t>
+          <t xml:space="preserve">Beginner Python </t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>DevOps: DSA 1 (New)</t>
+          <t>Devops: Beginner Python with Breaks (New)</t>
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/666</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/667</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
@@ -2241,18 +2220,18 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>DevOps: DSA 1 with Breaks (New)</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>652</v>
+          <t>DevOps: DSA 1 (New)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>666</v>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/652</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="inlineStr">
+          <t>https://www.scaler.com/scm/classes/edit-library/666</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -2282,20 +2261,20 @@
     <row r="6">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>Linux Shell Scripting and Computer Systems 1</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>DevOps: Linux 1 (Dec25)</t>
+          <t>Data Structure Algorithms 1</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>DevOps: DSA 1 with Breaks (New)</t>
         </is>
       </c>
       <c r="C6" s="19" t="n">
-        <v>752</v>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/752</t>
+        <v>652</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/652</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2305,43 +2284,43 @@
       </c>
       <c r="F6" s="24" t="n"/>
       <c r="G6" s="16" t="n"/>
-      <c r="H6" s="22" t="n"/>
-      <c r="I6" s="22" t="n"/>
-      <c r="J6" s="22" t="n"/>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="22" t="n"/>
-      <c r="M6" s="22" t="n"/>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="22" t="n"/>
-      <c r="P6" s="22" t="n"/>
-      <c r="Q6" s="22" t="n"/>
-      <c r="R6" s="22" t="n"/>
-      <c r="S6" s="22" t="n"/>
-      <c r="T6" s="22" t="n"/>
-      <c r="U6" s="22" t="n"/>
-      <c r="V6" s="22" t="n"/>
-      <c r="W6" s="22" t="n"/>
-      <c r="X6" s="22" t="n"/>
-      <c r="Y6" s="22" t="n"/>
-      <c r="Z6" s="22" t="n"/>
+      <c r="H6" s="38" t="n"/>
+      <c r="I6" s="38" t="n"/>
+      <c r="J6" s="38" t="n"/>
+      <c r="K6" s="38" t="n"/>
+      <c r="L6" s="38" t="n"/>
+      <c r="M6" s="38" t="n"/>
+      <c r="N6" s="38" t="n"/>
+      <c r="O6" s="38" t="n"/>
+      <c r="P6" s="38" t="n"/>
+      <c r="Q6" s="38" t="n"/>
+      <c r="R6" s="38" t="n"/>
+      <c r="S6" s="38" t="n"/>
+      <c r="T6" s="38" t="n"/>
+      <c r="U6" s="38" t="n"/>
+      <c r="V6" s="38" t="n"/>
+      <c r="W6" s="38" t="n"/>
+      <c r="X6" s="38" t="n"/>
+      <c r="Y6" s="38" t="n"/>
+      <c r="Z6" s="38" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>Linux Shell Scripting and Computer Systems 2</t>
+          <t>Linux Shell Scripting and Computer Systems 1</t>
         </is>
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>DevOps: Linux 2 (Dec25)</t>
+          <t>DevOps: Linux 1 (Dec25)</t>
         </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>753</v>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/753</t>
+        <v>752</v>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/752</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2351,43 +2330,43 @@
       </c>
       <c r="F7" s="24" t="n"/>
       <c r="G7" s="16" t="n"/>
-      <c r="H7" s="38" t="n"/>
-      <c r="I7" s="38" t="n"/>
-      <c r="J7" s="38" t="n"/>
-      <c r="K7" s="38" t="n"/>
-      <c r="L7" s="38" t="n"/>
-      <c r="M7" s="38" t="n"/>
-      <c r="N7" s="38" t="n"/>
-      <c r="O7" s="38" t="n"/>
-      <c r="P7" s="38" t="n"/>
-      <c r="Q7" s="38" t="n"/>
-      <c r="R7" s="38" t="n"/>
-      <c r="S7" s="38" t="n"/>
-      <c r="T7" s="38" t="n"/>
-      <c r="U7" s="38" t="n"/>
-      <c r="V7" s="38" t="n"/>
-      <c r="W7" s="38" t="n"/>
-      <c r="X7" s="38" t="n"/>
-      <c r="Y7" s="38" t="n"/>
-      <c r="Z7" s="38" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="22" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="22" t="n"/>
+      <c r="Z7" s="22" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>DevOps Tools 1</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>DevOps: DevOps Tools 1 (New)</t>
+          <t>Linux Shell Scripting and Computer Systems 2</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>DevOps: Linux 2 (Dec25)</t>
         </is>
       </c>
       <c r="C8" s="19" t="n">
-        <v>674</v>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/674</t>
+        <v>753</v>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/753</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -2420,20 +2399,20 @@
     <row r="9">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>DevOps Tools 2</t>
+          <t>DevOps Tools 1</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>DevOps: DevOps Tools 2 (New)</t>
+          <t>DevOps: DevOps Tools 1 (New)</t>
         </is>
       </c>
       <c r="C9" s="19" t="n">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/676</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/674</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -2466,25 +2445,29 @@
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>Career Readiness</t>
+          <t>DevOps Tools 2</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>DevOps: Career Readiness Contest</t>
+          <t>DevOps: DevOps Tools 2 (New)</t>
         </is>
       </c>
       <c r="C10" s="19" t="n">
-        <v>754</v>
+        <v>676</v>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/754</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="n"/>
+          <t>https://www.scaler.com/scm/classes/edit-library/676</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
       <c r="F10" s="24" t="n"/>
-      <c r="G10" s="17" t="n"/>
+      <c r="G10" s="16" t="n"/>
       <c r="H10" s="38" t="n"/>
       <c r="I10" s="38" t="n"/>
       <c r="J10" s="38" t="n"/>
@@ -2508,31 +2491,25 @@
     <row r="11">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>AWS 1</t>
+          <t>Career Readiness</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>NV Contests</t>
+          <t>DevOps: Career Readiness Contest</t>
         </is>
       </c>
       <c r="C11" s="19" t="n">
-        <v>592</v>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/592</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/754</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n"/>
       <c r="F11" s="24" t="n"/>
-      <c r="G11" s="19" t="n">
-        <v>2</v>
-      </c>
+      <c r="G11" s="17" t="n"/>
       <c r="H11" s="38" t="n"/>
       <c r="I11" s="38" t="n"/>
       <c r="J11" s="38" t="n"/>
@@ -2556,7 +2533,7 @@
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>AWS 2</t>
+          <t>AWS 1</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
@@ -2565,11 +2542,11 @@
         </is>
       </c>
       <c r="C12" s="19" t="n">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/593</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/592</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -2578,7 +2555,9 @@
         </is>
       </c>
       <c r="F12" s="24" t="n"/>
-      <c r="G12" s="16" t="n"/>
+      <c r="G12" s="19" t="n">
+        <v>2</v>
+      </c>
       <c r="H12" s="38" t="n"/>
       <c r="I12" s="38" t="n"/>
       <c r="J12" s="38" t="n"/>
@@ -2602,20 +2581,20 @@
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>DSA 3 &amp; 4</t>
+          <t>AWS 2</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>DevOps: DSA 3 &amp; 4 (New)</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C13" s="19" t="n">
-        <v>672</v>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/672</t>
+        <v>593</v>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/593</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -2648,25 +2627,25 @@
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>DSA 4</t>
+          <t>DSA 3 &amp; 4</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>DevOps: DSA 4 (Feb24 + Mar24)</t>
+          <t>DevOps: DSA 3 &amp; 4 (New)</t>
         </is>
       </c>
       <c r="C14" s="19" t="n">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/673</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/672</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>Live only once</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="F14" s="24" t="n"/>
@@ -2694,25 +2673,25 @@
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 2</t>
+          <t>DSA 4</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Devops: Data Structure Algorithms 2</t>
+          <t>DevOps: DSA 4 (Feb24 + Mar24)</t>
         </is>
       </c>
       <c r="C15" s="19" t="n">
-        <v>510</v>
+        <v>673</v>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/510</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/673</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Live only once</t>
         </is>
       </c>
       <c r="F15" s="24" t="n"/>
@@ -2740,23 +2719,27 @@
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>DevOps Breaks: DSA 1 &amp; 2</t>
+          <t>Data Structure Algorithms 2</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Devops: Data Structure Algorithms 2</t>
         </is>
       </c>
       <c r="C16" s="19" t="n">
-        <v>641</v>
+        <v>510</v>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/641</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="n"/>
+          <t>https://www.scaler.com/scm/classes/edit-library/510</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
       <c r="F16" s="24" t="n"/>
       <c r="G16" s="16" t="n"/>
       <c r="H16" s="38" t="n"/>
@@ -2782,27 +2765,23 @@
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>Foundations &amp; Network Security</t>
+          <t>Data Structure Algorithms 1 &amp; 2</t>
         </is>
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>DevOps: Foundations &amp; Network Security (Jan 2026)</t>
+          <t>DevOps Breaks: DSA 1 &amp; 2</t>
         </is>
       </c>
       <c r="C17" s="19" t="n">
-        <v>764</v>
+        <v>641</v>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/764</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
+          <t>https://www.scaler.com/scm/classes/edit-library/641</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="n"/>
       <c r="F17" s="24" t="n"/>
       <c r="G17" s="16" t="n"/>
       <c r="H17" s="38" t="n"/>
@@ -2828,20 +2807,20 @@
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>OS &amp; Infrastructure Security</t>
+          <t>Foundations &amp; Network Security</t>
         </is>
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>DevOps: OS &amp; Infrastructure Security (Jan 2026)</t>
+          <t>DevOps: Foundations &amp; Network Security (Jan 2026)</t>
         </is>
       </c>
       <c r="C18" s="19" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/765</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/764</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -2874,20 +2853,20 @@
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>Web, API, Application (VAPT) &amp; Cloud Security</t>
+          <t>OS &amp; Infrastructure Security</t>
         </is>
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>DevOps: Web, API, Application (VAPT) &amp; Cloud Security (Jan 2026)</t>
+          <t>DevOps: OS &amp; Infrastructure Security (Jan 2026)</t>
         </is>
       </c>
       <c r="C19" s="19" t="n">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/766</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/765</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -2920,20 +2899,20 @@
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRC, SOC &amp; Capstone (Blue + Red Team Integration) </t>
+          <t>Web, API, Application (VAPT) &amp; Cloud Security</t>
         </is>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>DevOps: GRC, SOC &amp; Capstone (Blue + Red Team Integration) (Jan 2026)</t>
+          <t>DevOps: Web, API, Application (VAPT) &amp; Cloud Security (Jan 2026)</t>
         </is>
       </c>
       <c r="C20" s="19" t="n">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/767</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/766</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -2964,33 +2943,31 @@
       <c r="Z20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Beginner Python </t>
-        </is>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>Devops: Beginner Python (NA)</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="n">
-        <v>497</v>
-      </c>
-      <c r="D21" s="29" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/497</t>
-        </is>
-      </c>
-      <c r="E21" s="35" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="30" t="n">
-        <v>1</v>
-      </c>
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRC, SOC &amp; Capstone (Blue + Red Team Integration) </t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>DevOps: GRC, SOC &amp; Capstone (Blue + Red Team Integration) (Jan 2026)</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>767</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/767</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="16" t="n"/>
       <c r="H21" s="38" t="n"/>
       <c r="I21" s="38" t="n"/>
       <c r="J21" s="38" t="n"/>
@@ -3014,20 +2991,20 @@
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>Beginner Python with Breaks</t>
+          <t xml:space="preserve">Beginner Python </t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Beginner Python (DevOps) with Breaks (NA)</t>
+          <t>Devops: Beginner Python (NA)</t>
         </is>
       </c>
       <c r="C22" s="28" t="n">
-        <v>586</v>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/586</t>
+        <v>497</v>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/497</t>
         </is>
       </c>
       <c r="E22" s="35" t="inlineStr">
@@ -3036,7 +3013,9 @@
         </is>
       </c>
       <c r="F22" s="35" t="n"/>
-      <c r="G22" s="9" t="n"/>
+      <c r="G22" s="30" t="n">
+        <v>1</v>
+      </c>
       <c r="H22" s="38" t="n"/>
       <c r="I22" s="38" t="n"/>
       <c r="J22" s="38" t="n"/>
@@ -3060,20 +3039,20 @@
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 1</t>
+          <t>Beginner Python with Breaks</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>DevOps: Data Structure Algorithms 1 (NA)</t>
+          <t>Beginner Python (DevOps) with Breaks (NA)</t>
         </is>
       </c>
       <c r="C23" s="28" t="n">
-        <v>506</v>
+        <v>586</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/506</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/586</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
@@ -3082,9 +3061,7 @@
         </is>
       </c>
       <c r="F23" s="35" t="n"/>
-      <c r="G23" s="30" t="n">
-        <v>2</v>
-      </c>
+      <c r="G23" s="9" t="n"/>
       <c r="H23" s="38" t="n"/>
       <c r="I23" s="38" t="n"/>
       <c r="J23" s="38" t="n"/>
@@ -3108,20 +3085,20 @@
     <row r="24">
       <c r="A24" s="35" t="inlineStr">
         <is>
-          <t>Data Stucture and Algorithms 1 with breaks</t>
+          <t>Data Structure Algorithms 1</t>
         </is>
       </c>
       <c r="B24" s="35" t="inlineStr">
         <is>
-          <t>DevOps: DSA 1with Breaks (NA)</t>
+          <t>DevOps: Data Structure Algorithms 1 (NA)</t>
         </is>
       </c>
       <c r="C24" s="28" t="n">
-        <v>587</v>
+        <v>506</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/587</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/506</t>
         </is>
       </c>
       <c r="E24" s="35" t="inlineStr">
@@ -3130,7 +3107,9 @@
         </is>
       </c>
       <c r="F24" s="35" t="n"/>
-      <c r="G24" s="9" t="n"/>
+      <c r="G24" s="30" t="n">
+        <v>2</v>
+      </c>
       <c r="H24" s="38" t="n"/>
       <c r="I24" s="38" t="n"/>
       <c r="J24" s="38" t="n"/>
@@ -3154,20 +3133,20 @@
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
         <is>
-          <t>Linux Shell Scripting and Computer Systems 1</t>
-        </is>
-      </c>
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>Devops: Linux Shell Scripting and Computer Systems - 1 (NA)</t>
+          <t>Data Stucture and Algorithms 1 with breaks</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>DevOps: DSA 1with Breaks (NA)</t>
         </is>
       </c>
       <c r="C25" s="28" t="n">
-        <v>436</v>
-      </c>
-      <c r="D25" s="29" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/436</t>
+        <v>587</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/587</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
@@ -3176,9 +3155,7 @@
         </is>
       </c>
       <c r="F25" s="35" t="n"/>
-      <c r="G25" s="28" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="G25" s="9" t="n"/>
       <c r="H25" s="38" t="n"/>
       <c r="I25" s="38" t="n"/>
       <c r="J25" s="38" t="n"/>
@@ -3202,20 +3179,20 @@
     <row r="26">
       <c r="A26" s="35" t="inlineStr">
         <is>
-          <t>Linux Shell Scripting and Computer Systems 2</t>
+          <t>Linux Shell Scripting and Computer Systems 1</t>
         </is>
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>Devops: Linux Shell Scripting and Computer Systems - 2 (NA)</t>
+          <t>Devops: Linux Shell Scripting and Computer Systems - 1 (NA)</t>
         </is>
       </c>
       <c r="C26" s="28" t="n">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/460</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/436</t>
         </is>
       </c>
       <c r="E26" s="35" t="inlineStr">
@@ -3224,7 +3201,9 @@
         </is>
       </c>
       <c r="F26" s="35" t="n"/>
-      <c r="G26" s="9" t="n"/>
+      <c r="G26" s="28" t="n">
+        <v>2.5</v>
+      </c>
       <c r="H26" s="38" t="n"/>
       <c r="I26" s="38" t="n"/>
       <c r="J26" s="38" t="n"/>
@@ -3248,20 +3227,20 @@
     <row r="27">
       <c r="A27" s="35" t="inlineStr">
         <is>
-          <t>Linux Shell Scripting and Computer Systems 3</t>
+          <t>Linux Shell Scripting and Computer Systems 2</t>
         </is>
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>Devops:Linux Shell Scripting and Computer Systems- 3 (NA)</t>
+          <t>Devops: Linux Shell Scripting and Computer Systems - 2 (NA)</t>
         </is>
       </c>
       <c r="C27" s="28" t="n">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/477</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/460</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
@@ -3299,15 +3278,15 @@
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>DevOps: Linux 3 (NA)</t>
+          <t>Devops:Linux Shell Scripting and Computer Systems- 3 (NA)</t>
         </is>
       </c>
       <c r="C28" s="28" t="n">
-        <v>654</v>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/654</t>
+        <v>477</v>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/477</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -3340,20 +3319,20 @@
     <row r="29">
       <c r="A29" s="35" t="inlineStr">
         <is>
-          <t>DevOps Tools 1</t>
-        </is>
-      </c>
-      <c r="B29" s="35" t="inlineStr">
-        <is>
-          <t>DevOps Tools -1</t>
+          <t>Linux Shell Scripting and Computer Systems 3</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>DevOps: Linux 3 (NA)</t>
         </is>
       </c>
       <c r="C29" s="28" t="n">
-        <v>509</v>
-      </c>
-      <c r="D29" s="29" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/509</t>
+        <v>654</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/654</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -3362,9 +3341,7 @@
         </is>
       </c>
       <c r="F29" s="35" t="n"/>
-      <c r="G29" s="30" t="n">
-        <v>3</v>
-      </c>
+      <c r="G29" s="9" t="n"/>
       <c r="H29" s="38" t="n"/>
       <c r="I29" s="38" t="n"/>
       <c r="J29" s="38" t="n"/>
@@ -3388,20 +3365,20 @@
     <row r="30">
       <c r="A30" s="35" t="inlineStr">
         <is>
-          <t>DevOps Tools 2</t>
+          <t>DevOps Tools 1</t>
         </is>
       </c>
       <c r="B30" s="35" t="inlineStr">
         <is>
-          <t>DevOps Tools -2</t>
+          <t>DevOps Tools -1</t>
         </is>
       </c>
       <c r="C30" s="28" t="n">
-        <v>548</v>
+        <v>509</v>
       </c>
       <c r="D30" s="29" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/548</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/509</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -3410,7 +3387,9 @@
         </is>
       </c>
       <c r="F30" s="35" t="n"/>
-      <c r="G30" s="9" t="n"/>
+      <c r="G30" s="30" t="n">
+        <v>3</v>
+      </c>
       <c r="H30" s="38" t="n"/>
       <c r="I30" s="38" t="n"/>
       <c r="J30" s="38" t="n"/>
@@ -3434,25 +3413,25 @@
     <row r="31">
       <c r="A31" s="35" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 3</t>
+          <t>DevOps Tools 2</t>
         </is>
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>Academy: DSA (Oct)</t>
+          <t>DevOps Tools -2</t>
         </is>
       </c>
       <c r="C31" s="28" t="n">
-        <v>277</v>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/277</t>
+        <v>548</v>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/548</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Not In Curriculum</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="F31" s="35" t="n"/>
@@ -3480,31 +3459,29 @@
     <row r="32">
       <c r="A32" s="35" t="inlineStr">
         <is>
-          <t>IaC</t>
+          <t>Data Structure Algorithms 3</t>
         </is>
       </c>
       <c r="B32" s="35" t="inlineStr">
         <is>
-          <t>DevOps: IaC (Not in Use)</t>
+          <t>Academy: DSA (Oct)</t>
         </is>
       </c>
       <c r="C32" s="28" t="n">
-        <v>643</v>
-      </c>
-      <c r="D32" s="29" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/643</t>
+        <v>277</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/277</t>
         </is>
       </c>
       <c r="E32" s="35" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>Not In Curriculum</t>
         </is>
       </c>
       <c r="F32" s="35" t="n"/>
-      <c r="G32" s="30" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="G32" s="9" t="n"/>
       <c r="H32" s="38" t="n"/>
       <c r="I32" s="38" t="n"/>
       <c r="J32" s="38" t="n"/>
@@ -3528,16 +3505,30 @@
     <row r="33">
       <c r="A33" s="35" t="inlineStr">
         <is>
-          <t>System Design</t>
-        </is>
-      </c>
-      <c r="B33" s="35" t="n"/>
-      <c r="C33" s="35" t="n"/>
-      <c r="D33" s="35" t="n"/>
-      <c r="E33" s="35" t="n"/>
+          <t>IaC</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>DevOps: IaC (Not in Use)</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n">
+        <v>643</v>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/643</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
       <c r="F33" s="35" t="n"/>
       <c r="G33" s="30" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="38" t="n"/>
       <c r="I33" s="38" t="n"/>
@@ -3562,7 +3553,7 @@
     <row r="34">
       <c r="A34" s="35" t="inlineStr">
         <is>
-          <t>Adv DSA</t>
+          <t>System Design</t>
         </is>
       </c>
       <c r="B34" s="35" t="n"/>
@@ -3571,7 +3562,7 @@
       <c r="E34" s="35" t="n"/>
       <c r="F34" s="35" t="n"/>
       <c r="G34" s="30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" s="38" t="n"/>
       <c r="I34" s="38" t="n"/>
@@ -3596,7 +3587,7 @@
     <row r="35">
       <c r="A35" s="35" t="inlineStr">
         <is>
-          <t>Ml Ops</t>
+          <t>Adv DSA</t>
         </is>
       </c>
       <c r="B35" s="35" t="n"/>
@@ -3605,7 +3596,7 @@
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="35" t="n"/>
       <c r="G35" s="30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35" s="38" t="n"/>
       <c r="I35" s="38" t="n"/>
@@ -3630,29 +3621,17 @@
     <row r="36">
       <c r="A36" s="35" t="inlineStr">
         <is>
-          <t>Linux Shell Scripting and Computer Systems 1</t>
-        </is>
-      </c>
-      <c r="B36" s="34" t="inlineStr">
-        <is>
-          <t>DevOps: Linux 1 (New) (NA)</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="n">
-        <v>650</v>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/650</t>
-        </is>
-      </c>
-      <c r="E36" s="35" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
+          <t>Ml Ops</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="n"/>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="35" t="n"/>
+      <c r="E36" s="35" t="n"/>
       <c r="F36" s="35" t="n"/>
-      <c r="G36" s="9" t="n"/>
+      <c r="G36" s="30" t="n">
+        <v>1</v>
+      </c>
       <c r="H36" s="38" t="n"/>
       <c r="I36" s="38" t="n"/>
       <c r="J36" s="38" t="n"/>
@@ -3676,20 +3655,20 @@
     <row r="37">
       <c r="A37" s="35" t="inlineStr">
         <is>
-          <t>Linux Shell Scripting and Computer Systems 2</t>
+          <t>Linux Shell Scripting and Computer Systems 1</t>
         </is>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>DevOps: Linux 2 (New) (NA)</t>
+          <t>DevOps: Linux 1 (New) (NA)</t>
         </is>
       </c>
       <c r="C37" s="28" t="n">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/651</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/650</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
@@ -3720,13 +3699,31 @@
       <c r="Z37" s="38" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="36" t="n"/>
-      <c r="B38" s="36" t="n"/>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="4" t="n"/>
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>Linux Shell Scripting and Computer Systems 2</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>DevOps: Linux 2 (New) (NA)</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n">
+        <v>651</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/651</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F38" s="35" t="n"/>
+      <c r="G38" s="9" t="n"/>
       <c r="H38" s="38" t="n"/>
       <c r="I38" s="38" t="n"/>
       <c r="J38" s="38" t="n"/>
@@ -3748,6 +3745,13 @@
       <c r="Z38" s="38" t="n"/>
     </row>
     <row r="39">
+      <c r="A39" s="36" t="n"/>
+      <c r="B39" s="36" t="n"/>
+      <c r="C39" s="36" t="n"/>
+      <c r="D39" s="36" t="n"/>
+      <c r="E39" s="36" t="n"/>
+      <c r="F39" s="36" t="n"/>
+      <c r="G39" s="4" t="n"/>
       <c r="H39" s="38" t="n"/>
       <c r="I39" s="38" t="n"/>
       <c r="J39" s="38" t="n"/>
@@ -24095,6 +24099,27 @@
       <c r="X1007" s="38" t="n"/>
       <c r="Y1007" s="38" t="n"/>
       <c r="Z1007" s="38" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="H1008" s="38" t="n"/>
+      <c r="I1008" s="38" t="n"/>
+      <c r="J1008" s="38" t="n"/>
+      <c r="K1008" s="38" t="n"/>
+      <c r="L1008" s="38" t="n"/>
+      <c r="M1008" s="38" t="n"/>
+      <c r="N1008" s="38" t="n"/>
+      <c r="O1008" s="38" t="n"/>
+      <c r="P1008" s="38" t="n"/>
+      <c r="Q1008" s="38" t="n"/>
+      <c r="R1008" s="38" t="n"/>
+      <c r="S1008" s="38" t="n"/>
+      <c r="T1008" s="38" t="n"/>
+      <c r="U1008" s="38" t="n"/>
+      <c r="V1008" s="38" t="n"/>
+      <c r="W1008" s="38" t="n"/>
+      <c r="X1008" s="38" t="n"/>
+      <c r="Y1008" s="38" t="n"/>
+      <c r="Z1008" s="38" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -2096,25 +2096,25 @@
       <c r="Z1" s="38" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Linux Shell Scripting and Computer Systems 2</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -3626,7 +3626,11 @@
       </c>
       <c r="B36" s="35" t="n"/>
       <c r="C36" s="35" t="n"/>
-      <c r="D36" s="35" t="n"/>
+      <c r="D36" s="35" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/650</t>
+        </is>
+      </c>
       <c r="E36" s="35" t="n"/>
       <c r="F36" s="35" t="n"/>
       <c r="G36" s="30" t="n">
@@ -24167,7 +24171,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z44"/>
+  <dimension ref="A1:Z45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="43" customWidth="1" style="46" min="1" max="1"/>
@@ -25164,20 +25168,20 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="0" t="inlineStr">
-        <is>
-          <t>DA ML 1</t>
-        </is>
-      </c>
-      <c r="B42" s="0" t="inlineStr">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Classical ML 2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C42" s="0" t="n">
+      <c r="C42" t="n">
         <v>338</v>
       </c>
-      <c r="D42" s="0" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
@@ -25186,7 +25190,7 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>DA ML 2</t>
+          <t>DA ML 1</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
@@ -25206,7 +25210,7 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>Advanced SQL</t>
+          <t>DA ML 2</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
@@ -25218,6 +25222,26 @@
         <v>338</v>
       </c>
       <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>Advanced SQL</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>NV Contests</t>
+          <t>Linux Certification Contest</t>
         </is>
       </c>
       <c r="C2" s="0" t="n">
@@ -25168,20 +25168,20 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>Classical ML 2</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>NV Contests</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -2075,7 +2075,11 @@
           <t>Months</t>
         </is>
       </c>
-      <c r="H1" s="38" t="n"/>
+      <c r="H1" s="38" t="inlineStr">
+        <is>
+          <t>Skill Eval Label</t>
+        </is>
+      </c>
       <c r="I1" s="38" t="n"/>
       <c r="J1" s="38" t="n"/>
       <c r="K1" s="38" t="n"/>
@@ -2117,6 +2121,11 @@
       <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Live</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Linux Certification Contest</t>
         </is>
       </c>
     </row>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -2107,7 +2107,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>Linux Certification Contest</t>
+          <t>NV Contests</t>
         </is>
       </c>
       <c r="C2" s="0" t="n">
@@ -2123,7 +2123,7 @@
           <t>Live</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>Linux Certification Contest</t>
         </is>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -602,6 +602,11 @@
           <t>Num Attempts</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Skill Eval Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1969,6 +1974,11 @@
       <c r="C76" s="0" t="inlineStr">
         <is>
           <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Back-end development- Neovarsity contest</t>
         </is>
       </c>
     </row>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -602,7 +602,7 @@
           <t>Num Attempts</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>Skill Eval Label</t>
         </is>
@@ -1976,7 +1976,7 @@
           <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="0" t="inlineStr">
         <is>
           <t>Back-end development- Neovarsity contest</t>
         </is>
@@ -24234,7 +24234,11 @@
           <t>Months</t>
         </is>
       </c>
-      <c r="H1" s="37" t="n"/>
+      <c r="H1" s="37" t="inlineStr">
+        <is>
+          <t>Skill Eval Label</t>
+        </is>
+      </c>
       <c r="I1" s="37" t="n"/>
       <c r="J1" s="37" t="n"/>
       <c r="K1" s="37" t="n"/>
@@ -24870,11 +24874,16 @@
         </is>
       </c>
       <c r="C30" s="40" t="n">
-        <v>60</v>
+        <v>338</v>
       </c>
       <c r="D30" s="41" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/scm/classes/edit-library/60</t>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DSML Module Test: Computer Vision (No Class Today)</t>
         </is>
       </c>
     </row>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -2234,7 +2234,7 @@
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 1</t>
+          <t>Data Structure Algorithms 1 (DevOps)</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
@@ -2280,7 +2280,7 @@
     <row r="6">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 1</t>
+          <t>Data Structure Algorithms 1 (DevOps)</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
@@ -2738,7 +2738,7 @@
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 2</t>
+          <t>Data Structure Algorithms 2 (DevOps)</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
@@ -3104,7 +3104,7 @@
     <row r="24">
       <c r="A24" s="35" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 1</t>
+          <t>Data Structure Algorithms 1 (DevOps)</t>
         </is>
       </c>
       <c r="B24" s="35" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="32">
       <c r="A32" s="35" t="inlineStr">
         <is>
-          <t>Data Structure Algorithms 3</t>
+          <t>Data Structure Algorithms 3 (DevOps)</t>
         </is>
       </c>
       <c r="B32" s="35" t="inlineStr">
@@ -24881,7 +24881,7 @@
           <t>https://www.scaler.com/scm/classes/edit-library/338</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
         <is>
           <t>DSML Module Test: Computer Vision (No Class Today)</t>
         </is>

--- a/data/Library__All_Programs.xlsx
+++ b/data/Library__All_Programs.xlsx
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z76"/>
+  <dimension ref="A1:Z77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="40.88" customWidth="1" style="46" min="1" max="1"/>
@@ -1979,6 +1979,28 @@
       <c r="E76" s="0" t="inlineStr">
         <is>
           <t>Back-end development- Neovarsity contest</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AI &amp; Agents: From Talking to AI to Building One</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NV Contests</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/scm/classes/edit-library/338</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AI &amp; Agents: From Talking to AI to Building One Contest</t>
         </is>
       </c>
     </row>
